--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7C41D-F302-4E58-8309-8CE94BBA0FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEA07B9-E69A-4FD2-8B8C-756F285DB9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>对象</t>
   </si>
@@ -99,6 +99,14 @@
   </si>
   <si>
     <t>命令端接入批量激活、设置白名单、连接，并附带二次确认机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨区块强制加载票据停服前自动清理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -446,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -677,6 +685,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEA07B9-E69A-4FD2-8B8C-756F285DB9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0831B887-18C6-4481-935C-C67DE7517C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t>对象</t>
   </si>
@@ -103,6 +103,30 @@
   </si>
   <si>
     <t>跨区块强制加载票据停服前自动清理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语义中转扩大覆盖P0-P2、P2测试面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本层语义严格对齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令层输入剪枝，严格对齐，大小写兼容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置层严格对齐，大小写兼容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -454,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -696,6 +720,38 @@
         <v>27</v>
       </c>
     </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0831B887-18C6-4481-935C-C67DE7517C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AC6C92-8903-41BE-8087-16DCA939D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
   <si>
     <t>对象</t>
   </si>
@@ -126,11 +126,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>配置层严格对齐，大小写兼容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置层严格对齐，大小写兼容，通过中转标准分支</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -728,7 +728,7 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,6 +749,9 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
         <v>32</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AC6C92-8903-41BE-8087-16DCA939D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278A3C4E-B0A2-47A9-9FD4-A2896E020E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
   <si>
     <t>对象</t>
   </si>
@@ -131,6 +131,10 @@
   </si>
   <si>
     <t>配置层严格对齐，大小写兼容，通过中转标准分支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码层命名统一对齐P0-P2+去壳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -478,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -755,6 +759,14 @@
         <v>32</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278A3C4E-B0A2-47A9-9FD4-A2896E020E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74B2CE6-1C17-48FD-9129-C90E81B486C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
   <si>
     <t>对象</t>
   </si>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>代码层命名统一对齐P0-P2+去壳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络协议/持久化层对齐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -750,6 +754,9 @@
       <c r="B25" t="s">
         <v>28</v>
       </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -758,12 +765,29 @@
       <c r="B26" t="s">
         <v>32</v>
       </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
         <v>32</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74B2CE6-1C17-48FD-9129-C90E81B486C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63DC38C-27C3-49AF-AE09-55B4A846FBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
   <si>
     <t>对象</t>
   </si>
@@ -139,6 +139,14 @@
   </si>
   <si>
     <t>网络协议/持久化层对齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除语义偏差遗留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补齐自动化测试覆盖率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -791,6 +799,28 @@
         <v>32</v>
       </c>
     </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63DC38C-27C3-49AF-AE09-55B4A846FBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8232B0D9-F19D-48CD-90BC-74B832F2D2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5568" yWindow="2940" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
   <si>
     <t>对象</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>补齐自动化测试覆盖率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加强制加载区块常驻入口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常驻设置下线提醒，退役清理白名单，显示补齐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -821,6 +833,22 @@
         <v>32</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8232B0D9-F19D-48CD-90BC-74B832F2D2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C369A9F3-768A-4B75-9267-615BF831B762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5568" yWindow="2940" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="42">
   <si>
     <t>对象</t>
   </si>
@@ -159,6 +159,10 @@
   </si>
   <si>
     <t>常驻设置下线提醒，退役清理白名单，显示补齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩浆毁坏无法自动退役问题回归</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -506,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -848,6 +852,17 @@
       <c r="A32" t="s">
         <v>40</v>
       </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C369A9F3-768A-4B75-9267-615BF831B762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E735D57-094C-42AC-ACA5-1C952F0C3EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5568" yWindow="2940" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>对象</t>
   </si>
@@ -162,7 +162,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>岩浆毁坏无法自动退役问题回归</t>
+    <t>销毁无法自动退役问题回归修复+补齐回归测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,9 +859,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E735D57-094C-42AC-ACA5-1C952F0C3EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB6468F-8435-4EFE-B0CF-35C284720000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5568" yWindow="2940" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="4356" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
   <si>
     <t>对象</t>
   </si>
@@ -163,6 +163,18 @@
   </si>
   <si>
     <t>销毁无法自动退役问题回归修复+补齐回归测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令根权限可配置+状态语义优化，便于F3观察核心红石粉的激活源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令、gui、跨区块、配置出入口和关键逻辑补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui/命令代码优化，减少冗余</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -870,6 +882,33 @@
         <v>39</v>
       </c>
     </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB6468F-8435-4EFE-B0CF-35C284720000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912FA6E6-F64F-4F62-B168-0990A35C7045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="4356" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
   <si>
     <t>对象</t>
   </si>
@@ -908,6 +908,12 @@
       <c r="A36" t="s">
         <v>44</v>
       </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912FA6E6-F64F-4F62-B168-0990A35C7045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFB138B-9C0C-4E8E-9C4A-A310E4860C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="4356" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="46">
   <si>
     <t>对象</t>
   </si>
@@ -175,6 +175,10 @@
   </si>
   <si>
     <t>gui/命令代码优化，减少冗余</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶面核心红石粉active客户端更新节流避免邻居更新风暴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -522,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -915,6 +919,17 @@
         <v>39</v>
       </c>
     </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFB138B-9C0C-4E8E-9C4A-A310E4860C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505899E3-B4D1-437E-BDED-DF1E554247EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="4356" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6828" yWindow="2964" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
   <si>
     <t>对象</t>
   </si>
@@ -179,6 +179,14 @@
   </si>
   <si>
     <t>顶面核心红石粉active客户端更新节流避免邻居更新风暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枚举语义对齐/语义中转收紧/active显式构造false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -930,6 +938,17 @@
         <v>39</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505899E3-B4D1-437E-BDED-DF1E554247EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F472E6C3-C9AF-4C09-BCE4-DA671C7DAC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6828" yWindow="2964" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="51">
   <si>
     <t>对象</t>
   </si>
@@ -187,6 +187,18 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待退役持久化镜像避免跨重启丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分离mixins，优先开发no-mixin(核心功能)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -949,6 +961,22 @@
         <v>47</v>
       </c>
     </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F472E6C3-C9AF-4C09-BCE4-DA671C7DAC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0557E5-2AC8-4C9E-ABFD-FB13251FD1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6828" yWindow="2964" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="52">
   <si>
     <t>对象</t>
   </si>
@@ -199,6 +199,10 @@
   </si>
   <si>
     <t>分离mixins，优先开发no-mixin(核心功能)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -976,6 +980,12 @@
       <c r="A40" t="s">
         <v>50</v>
       </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0557E5-2AC8-4C9E-ABFD-FB13251FD1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486324E-9C56-4555-849D-D138F2A3FBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6828" yWindow="2964" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4332" yWindow="3552" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
   <si>
     <t>对象</t>
   </si>
@@ -203,6 +203,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更改发布名配置+去除锂的相关诊断设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -550,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -987,6 +991,17 @@
         <v>51</v>
       </c>
     </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486324E-9C56-4555-849D-D138F2A3FBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DABEB46-7D46-414B-815C-4FA7C38623AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4332" yWindow="3552" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
   <si>
     <t>对象</t>
   </si>
@@ -207,6 +207,10 @@
   </si>
   <si>
     <t>更改发布名配置+去除锂的相关诊断设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心粉通知量收敛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -554,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1002,6 +1006,17 @@
         <v>51</v>
       </c>
     </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DABEB46-7D46-414B-815C-4FA7C38623AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704F60B0-10AB-4064-AFBD-876D8EA7D85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4332" yWindow="3552" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t>对象</t>
   </si>
@@ -211,6 +211,14 @@
   </si>
   <si>
     <t>核心粉通知量收敛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远外显+近外显、按键切换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1017,6 +1025,17 @@
         <v>51</v>
       </c>
     </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704F60B0-10AB-4064-AFBD-876D8EA7D85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7D8604-E874-4027-A7E0-2534ED53DC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4332" yWindow="3552" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1404" yWindow="3732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="59">
   <si>
     <t>对象</t>
   </si>
@@ -214,11 +214,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>远外显+近外显、按键切换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远外显+近外显、按键切换/材质更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>退役同步外显序号补全+渲染代码优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限矩阵分析+基本写入权限控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加连接信息显示的可配置+名单权限设置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -566,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1027,13 +1039,40 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
         <v>54</v>
       </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7D8604-E874-4027-A7E0-2534ED53DC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0BAC67-CD63-4934-AE8F-67CDF1365EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1404" yWindow="3732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="63">
   <si>
     <t>对象</t>
   </si>
@@ -231,6 +231,22 @@
   </si>
   <si>
     <t>添加连接信息显示的可配置+名单权限设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐私节点剔除出相关连接对象的连接列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>link/node get接入隐私受控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现增量修改关系/增量式底层实现+set_Links重构到link下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1072,6 +1088,36 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0BAC67-CD63-4934-AE8F-67CDF1365EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE20C74D-13C5-4214-BEA5-574214B70E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t>对象</t>
   </si>
@@ -226,10 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>权限矩阵分析+基本写入权限控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>添加连接信息显示的可配置+名单权限设置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -247,6 +243,14 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他权限管控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本写入权限控制/隐藏权限具体要求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1077,7 +1081,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -1088,7 +1092,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -1099,7 +1103,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -1107,18 +1111,29 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
         <v>61</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>62</v>
-      </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE20C74D-13C5-4214-BEA5-574214B70E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F0AD7F-97C6-4C2D-8114-542755E3309C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
   <si>
     <t>对象</t>
   </si>
@@ -251,6 +251,10 @@
   </si>
   <si>
     <t>基本写入权限控制/隐藏权限具体要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一命令架构：连接读写控制/激活、退役</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -598,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1136,6 +1140,17 @@
         <v>62</v>
       </c>
     </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F0AD7F-97C6-4C2D-8114-542755E3309C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B47905-22BF-4641-B4AF-F32672302DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>对象</t>
   </si>
@@ -1139,6 +1139,12 @@
       <c r="A50" t="s">
         <v>62</v>
       </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B47905-22BF-4641-B4AF-F32672302DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B70493B-0EB0-4A8B-B780-121DC9EF3CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
   <si>
     <t>对象</t>
   </si>
@@ -255,6 +255,10 @@
   </si>
   <si>
     <t>统一命令架构：连接读写控制/激活、退役</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务端批量数量上限配置服务端统一裁决</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1157,6 +1161,14 @@
         <v>61</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B70493B-0EB0-4A8B-B780-121DC9EF3CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E521B9-9B12-4F94-B05B-49695DC354FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="68">
   <si>
     <t>对象</t>
   </si>
@@ -259,6 +259,14 @@
   </si>
   <si>
     <t>服务端批量数量上限配置服务端统一裁决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心粉去原版依赖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令攻击防护</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1169,6 +1177,22 @@
         <v>61</v>
       </c>
     </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E521B9-9B12-4F94-B05B-49695DC354FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DCB20C-7150-4A7C-B860-C87E5ED32FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="69">
   <si>
     <t>对象</t>
   </si>
@@ -267,6 +267,10 @@
   </si>
   <si>
     <t>命令攻击防护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接切换按钮改为连接同步拉杆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -614,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1193,6 +1197,14 @@
         <v>67</v>
       </c>
     </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DCB20C-7150-4A7C-B860-C87E5ED32FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3904262B-DAC2-40AA-895A-62CA88D2C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
   <si>
     <t>对象</t>
   </si>
@@ -271,6 +271,14 @@
   </si>
   <si>
     <t>连接切换按钮改为连接同步拉杆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接同步按钮所有命名对齐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -618,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1196,6 +1204,12 @@
       <c r="A54" t="s">
         <v>67</v>
       </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -1203,6 +1217,20 @@
       </c>
       <c r="B55" t="s">
         <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3904262B-DAC2-40AA-895A-62CA88D2C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867F723F-E196-48CF-8F30-0EB3A2D84E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="77">
   <si>
     <t>对象</t>
   </si>
@@ -279,6 +279,30 @@
   </si>
   <si>
     <t>连接同步按钮所有命名对齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强p0-p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强p2-p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强p4-p5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强p6-p7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强*p8-p9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心粉去原版依赖补做</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -626,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1233,6 +1257,42 @@
         <v>69</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867F723F-E196-48CF-8F30-0EB3A2D84E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431289FB-EB06-4281-813F-20537CCE41A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
   <si>
     <t>对象</t>
   </si>
@@ -1272,6 +1272,12 @@
       <c r="A58" t="s">
         <v>72</v>
       </c>
+      <c r="B58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431289FB-EB06-4281-813F-20537CCE41A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D03277D-9032-4F98-90E2-B5965B1E5841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
   <si>
     <t>对象</t>
   </si>
@@ -1283,6 +1283,9 @@
       <c r="A59" t="s">
         <v>73</v>
       </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D03277D-9032-4F98-90E2-B5965B1E5841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AF05A6-44F1-4E0C-9722-3DCEE1F0BE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="78">
   <si>
     <t>对象</t>
   </si>
@@ -303,6 +303,10 @@
   </si>
   <si>
     <t>核心粉去原版依赖补做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1283,6 +1287,9 @@
       <c r="A59" t="s">
         <v>73</v>
       </c>
+      <c r="B59" t="s">
+        <v>77</v>
+      </c>
       <c r="C59" t="s">
         <v>69</v>
       </c>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AF05A6-44F1-4E0C-9722-3DCEE1F0BE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAFDAB9-3FE1-41F5-A05E-C54117140BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAFDAB9-3FE1-41F5-A05E-C54117140BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E29C34C-AA46-4429-8D92-9E8EDA2E9C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>对象</t>
   </si>
@@ -303,6 +303,10 @@
   </si>
   <si>
     <t>核心粉去原版依赖补做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1308,6 +1312,12 @@
       <c r="A62" t="s">
         <v>76</v>
       </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E29C34C-AA46-4429-8D92-9E8EDA2E9C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB42F5-F59B-4B43-80B0-8A2F97CA6468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5868" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
   <si>
     <t>对象</t>
   </si>
@@ -294,10 +294,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>信号链路一致性增强p6-p7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>信号链路一致性增强*p8-p9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -311,6 +307,26 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号链路一致性增强p6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pulse/toggle无限期中继实验性玩法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分段递增中继派送重试间隔+目标区块加载主动唤醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复sync跨区块补发时间键引用错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1292,7 +1308,7 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
         <v>69</v>
@@ -1300,23 +1316,56 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>78</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="C65" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB42F5-F59B-4B43-80B0-8A2F97CA6468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9744EDB8-9229-4B08-ACC1-0BE32A839E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
   <si>
     <t>对象</t>
   </si>
@@ -327,6 +327,10 @@
   </si>
   <si>
     <t>修复sync跨区块补发时间键引用错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构化真值变化即标dirty</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -674,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1348,6 +1352,9 @@
       <c r="B63" t="s">
         <v>79</v>
       </c>
+      <c r="C63" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1364,7 +1371,21 @@
       <c r="A65" t="s">
         <v>82</v>
       </c>
+      <c r="B65" t="s">
+        <v>79</v>
+      </c>
       <c r="C65" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" t="s">
         <v>79</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9744EDB8-9229-4B08-ACC1-0BE32A839E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94219C1-C283-4D5E-BA66-ED1E3B2442F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="86">
   <si>
     <t>对象</t>
   </si>
@@ -331,6 +331,14 @@
   </si>
   <si>
     <t>结构化真值变化即标dirty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1对多高频并发优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏测试场景构建</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -678,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1389,6 +1397,16 @@
         <v>79</v>
       </c>
     </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94219C1-C283-4D5E-BA66-ED1E3B2442F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8B6D50-6CCE-4DD6-B0BB-2401FFC5CC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="86">
   <si>
     <t>对象</t>
   </si>
@@ -338,7 +338,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>游戏测试场景构建</t>
+    <t>游戏自动测试场景骨架构建</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1406,6 +1406,9 @@
       <c r="A68" t="s">
         <v>85</v>
       </c>
+      <c r="C68" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8B6D50-6CCE-4DD6-B0BB-2401FFC5CC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52667E2B-E661-4EA6-890C-A686B0FBE5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
   <si>
     <t>对象</t>
   </si>
@@ -339,6 +339,14 @@
   </si>
   <si>
     <t>游戏自动测试场景骨架构建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原有命令改造无玩家模式供测试用p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原有命令改造无玩家模式供测试用p2/添加状态IO命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -686,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1410,6 +1418,19 @@
         <v>79</v>
       </c>
     </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52667E2B-E661-4EA6-890C-A686B0FBE5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B2D4C3-C0D9-4BDF-B88C-6C9E7CB953E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="2652" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4212" yWindow="3084" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="91">
   <si>
     <t>对象</t>
   </si>
@@ -346,7 +346,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>原有命令改造无玩家模式供测试用p2/添加状态IO命令</t>
+    <t>原有命令改造无玩家模式供测试用p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加状态IO采样器，支持命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内自动化扩展一例一档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p3.模拟输入器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1431,6 +1443,24 @@
         <v>87</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B2D4C3-C0D9-4BDF-B88C-6C9E7CB953E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF4E10-33DE-4350-87C6-B7555B3A5F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4212" yWindow="3084" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
   <si>
     <t>对象</t>
   </si>
@@ -1447,6 +1447,12 @@
       <c r="A71" t="s">
         <v>88</v>
       </c>
+      <c r="B71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF4E10-33DE-4350-87C6-B7555B3A5F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C64B33-57FC-4522-8EC4-2C5C122F6827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="3084" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -358,7 +358,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>p3.模拟输入器</t>
+    <t>基本拟输入器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C64B33-57FC-4522-8EC4-2C5C122F6827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEAB53A-477B-47B2-97F4-6CD7478AC9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>对象</t>
   </si>
@@ -334,10 +334,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1对多高频并发优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>游戏自动测试场景骨架构建</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -359,6 +355,14 @@
   </si>
   <si>
     <t>基本拟输入器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理历史遗留语义设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -706,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1417,14 +1421,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>84</v>
-      </c>
-    </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
         <v>79</v>
@@ -1432,7 +1431,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
         <v>79</v>
@@ -1440,12 +1439,12 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
         <v>79</v>
@@ -1456,7 +1455,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
         <v>79</v>
@@ -1464,6 +1463,17 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" t="s">
         <v>90</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEAB53A-477B-47B2-97F4-6CD7478AC9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5097659E-3E51-4157-8A1D-EBAEB7E97043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="95">
   <si>
     <t>对象</t>
   </si>
@@ -363,6 +363,18 @@
   </si>
   <si>
     <t>清理历史遗留语义设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复输入器跨重启遗留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化输入器跨重启遗留清理并可配置隔离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -370,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +396,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFABB2BF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -406,8 +424,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -710,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1477,8 +1498,28 @@
         <v>90</v>
       </c>
     </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5097659E-3E51-4157-8A1D-EBAEB7E97043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F484747-D6FB-46DF-B504-36D4ECB6C098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="99">
   <si>
     <t>对象</t>
   </si>
@@ -375,6 +375,22 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码组织结构优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令参数解析优化完全覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快照整合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采集器扩展</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +398,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,12 +412,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFABB2BF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -426,8 +436,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -731,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1442,9 +1452,17 @@
         <v>79</v>
       </c>
     </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
         <v>79</v>
@@ -1452,23 +1470,23 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>85</v>
-      </c>
-      <c r="C69" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="B70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
         <v>79</v>
@@ -1476,45 +1494,63 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
+      <c r="A75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F484747-D6FB-46DF-B504-36D4ECB6C098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2191BEFC-F8FE-42CD-AF42-DD763C427FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="99">
   <si>
     <t>对象</t>
   </si>
@@ -1552,6 +1552,12 @@
       <c r="A79" t="s">
         <v>98</v>
       </c>
+      <c r="B79" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2191BEFC-F8FE-42CD-AF42-DD763C427FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4783DC-5BF0-41FC-84BA-3A6A1F8CB7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
   <si>
     <t>对象</t>
   </si>
@@ -1555,9 +1555,6 @@
       <c r="B79" t="s">
         <v>94</v>
       </c>
-      <c r="C79" t="s">
-        <v>94</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4783DC-5BF0-41FC-84BA-3A6A1F8CB7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D8AA22-61A8-41E4-AC96-57958BC624AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="100">
   <si>
     <t>对象</t>
   </si>
@@ -354,10 +354,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基本拟输入器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -391,6 +387,14 @@
   </si>
   <si>
     <t>采集器扩展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本输入器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1494,66 +1498,72 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s">
         <v>93</v>
       </c>
-      <c r="B75" t="s">
-        <v>94</v>
-      </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" t="s">
         <v>98</v>
-      </c>
-      <c r="B79" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D8AA22-61A8-41E4-AC96-57958BC624AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5EE7F4-9E76-4BCC-AB5F-244B21D38EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
   <si>
     <t>对象</t>
   </si>
@@ -1549,6 +1549,9 @@
       <c r="A77" t="s">
         <v>95</v>
       </c>
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5EE7F4-9E76-4BCC-AB5F-244B21D38EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B716D0AE-1CC2-406D-8E9E-86D74FE036EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="100">
   <si>
     <t>对象</t>
   </si>
@@ -342,10 +342,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>原有命令改造无玩家模式供测试用p2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>添加状态IO采样器，支持命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,6 +391,10 @@
   </si>
   <si>
     <t>基本输入器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接按钮、拉杆核心粉远近外显优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1476,35 +1476,41 @@
       <c r="A69" t="s">
         <v>86</v>
       </c>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>87</v>
       </c>
-      <c r="B70" t="s">
-        <v>79</v>
-      </c>
       <c r="C70" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>98</v>
+      </c>
+      <c r="B71" t="s">
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1512,31 +1518,25 @@
         <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="A75" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1544,29 +1544,38 @@
       <c r="A76" t="s">
         <v>94</v>
       </c>
+      <c r="B76" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>95</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>96</v>
       </c>
+      <c r="B78" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" t="s">
         <v>97</v>
       </c>
-      <c r="B79" t="s">
-        <v>93</v>
-      </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B716D0AE-1CC2-406D-8E9E-86D74FE036EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10868507-EC8C-47F8-942D-41F606815F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5712" yWindow="3108" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="100">
   <si>
     <t>对象</t>
   </si>
@@ -370,10 +370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>代码组织结构优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>命令参数解析优化完全覆盖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,6 +391,10 @@
   </si>
   <si>
     <t>连接按钮、拉杆核心粉远近外显优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
         <v>92</v>
@@ -1537,45 +1537,48 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>99</v>
+      </c>
+      <c r="C75" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
         <v>92</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10868507-EC8C-47F8-942D-41F606815F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE8BD73-B8A0-4963-B0C6-DC8E988AC6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="101">
   <si>
     <t>对象</t>
   </si>
@@ -395,6 +395,10 @@
   </si>
   <si>
     <t>代码重构p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -745,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1539,6 +1543,9 @@
       <c r="A75" t="s">
         <v>99</v>
       </c>
+      <c r="B75" t="s">
+        <v>96</v>
+      </c>
       <c r="C75" t="s">
         <v>96</v>
       </c>
@@ -1578,6 +1585,17 @@
         <v>96</v>
       </c>
       <c r="C79" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" t="s">
         <v>96</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE8BD73-B8A0-4963-B0C6-DC8E988AC6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AE74A0-E096-47E5-B35A-C3E027425962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
   <si>
     <t>对象</t>
   </si>
@@ -399,6 +399,10 @@
   </si>
   <si>
     <t>代码重构p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -749,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1599,6 +1603,14 @@
         <v>96</v>
       </c>
     </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AE74A0-E096-47E5-B35A-C3E027425962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBDA22D-065B-4D6F-9124-A8152798D9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="104">
   <si>
     <t>对象</t>
   </si>
@@ -403,6 +403,14 @@
   </si>
   <si>
     <t>代码重构p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1607,8 +1615,22 @@
       <c r="A81" t="s">
         <v>101</v>
       </c>
+      <c r="B81" t="s">
+        <v>103</v>
+      </c>
       <c r="C81" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" t="s">
+        <v>103</v>
+      </c>
+      <c r="C82" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBDA22D-065B-4D6F-9124-A8152798D9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F772E2FF-381B-4119-A07D-189AB3817BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
   <si>
     <t>对象</t>
   </si>
@@ -407,6 +407,14 @@
   </si>
   <si>
     <t>代码重构p4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -761,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1633,6 +1641,17 @@
         <v>103</v>
       </c>
     </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>104</v>
+      </c>
+      <c r="B83" t="s">
+        <v>105</v>
+      </c>
+      <c r="C83" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F772E2FF-381B-4119-A07D-189AB3817BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE5A473-EB88-4AE2-9207-88C8686FF2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="107">
   <si>
     <t>对象</t>
   </si>
@@ -419,6 +419,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -769,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1652,6 +1656,17 @@
         <v>105</v>
       </c>
     </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>106</v>
+      </c>
+      <c r="B84" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE5A473-EB88-4AE2-9207-88C8686FF2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DDE86A-99D8-4A5D-B287-1B16C01933DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="108">
   <si>
     <t>对象</t>
   </si>
@@ -423,6 +423,10 @@
   </si>
   <si>
     <t>代码重构p6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码重构p7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -773,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1667,6 +1671,11 @@
         <v>105</v>
       </c>
     </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DDE86A-99D8-4A5D-B287-1B16C01933DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E68CDF6-7A45-4E03-94FD-5B60E17E2806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E68CDF6-7A45-4E03-94FD-5B60E17E2806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE10F0E9-B11F-43A4-99DD-A3B25D11FBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="109">
   <si>
     <t>对象</t>
   </si>
@@ -427,6 +427,10 @@
   </si>
   <si>
     <t>代码重构p7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1675,6 +1679,9 @@
       <c r="A85" t="s">
         <v>107</v>
       </c>
+      <c r="C85" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE10F0E9-B11F-43A4-99DD-A3B25D11FBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C2B2C2-18C0-4D83-B0AA-D7CDD9D453E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
   <si>
     <t>对象</t>
   </si>
@@ -427,6 +427,14 @@
   </si>
   <si>
     <t>代码重构p7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内性能测试激活问题修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -781,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1683,6 +1691,14 @@
         <v>108</v>
       </c>
     </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C2B2C2-18C0-4D83-B0AA-D7CDD9D453E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF4E8C-58F7-4119-9114-53B4C96A9493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="113">
   <si>
     <t>对象</t>
   </si>
@@ -435,6 +435,14 @@
   </si>
   <si>
     <t>游戏内性能测试激活问题修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户端自启进服</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -789,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1605,6 +1613,9 @@
       <c r="B77" t="s">
         <v>96</v>
       </c>
+      <c r="C77" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1697,6 +1708,14 @@
       </c>
       <c r="C86" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF4E8C-58F7-4119-9114-53B4C96A9493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649A7E29-339B-4CDB-8409-68C6E5191BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="115">
   <si>
     <t>对象</t>
   </si>
@@ -443,6 +443,14 @@
   </si>
   <si>
     <t>客户端自启进服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bench设置连接优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -797,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1718,6 +1726,17 @@
         <v>112</v>
       </c>
     </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" t="s">
+        <v>114</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649A7E29-339B-4CDB-8409-68C6E5191BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0C8F9A-4DF3-43D5-AEF0-6BC61AF59A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="118">
   <si>
     <t>对象</t>
   </si>
@@ -451,6 +451,18 @@
   </si>
   <si>
     <t>bench设置连接优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内补测p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内补测p2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -805,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1737,6 +1749,22 @@
         <v>114</v>
       </c>
     </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>116</v>
+      </c>
+      <c r="C90" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0C8F9A-4DF3-43D5-AEF0-6BC61AF59A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF385801-A32D-4361-927D-DCC2F4EC7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="118">
   <si>
     <t>对象</t>
   </si>
@@ -1761,6 +1761,9 @@
       <c r="A90" t="s">
         <v>116</v>
       </c>
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
       <c r="C90" t="s">
         <v>117</v>
       </c>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF385801-A32D-4361-927D-DCC2F4EC7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22880DB-A43F-4DB6-B319-C23176AEC26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="119">
   <si>
     <t>对象</t>
   </si>
@@ -467,6 +467,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复实时探针阻塞式实现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -817,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1768,6 +1772,17 @@
         <v>117</v>
       </c>
     </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22880DB-A43F-4DB6-B319-C23176AEC26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08FCD64-DA02-4A4D-8BFE-7A4FD1F8E98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="120">
   <si>
     <t>对象</t>
   </si>
@@ -471,6 +471,10 @@
   </si>
   <si>
     <t>修复实时探针阻塞式实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内补测p3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -821,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1783,6 +1787,11 @@
         <v>117</v>
       </c>
     </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08FCD64-DA02-4A4D-8BFE-7A4FD1F8E98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46162727-7B75-4067-9166-6958B230BBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="120">
   <si>
     <t>对象</t>
   </si>
@@ -1791,6 +1791,9 @@
       <c r="A92" t="s">
         <v>119</v>
       </c>
+      <c r="C92" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46162727-7B75-4067-9166-6958B230BBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D992F31-8966-4E0C-9537-5310CB26FC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="121">
   <si>
     <t>对象</t>
   </si>
@@ -475,6 +475,10 @@
   </si>
   <si>
     <t>游戏内补测p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏内测试封装</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -825,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1795,6 +1799,11 @@
         <v>117</v>
       </c>
     </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D992F31-8966-4E0C-9537-5310CB26FC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49805F4B-7F19-498A-AC71-2CD4C1185F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="122">
   <si>
     <t>对象</t>
   </si>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>游戏内测试封装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -829,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1804,6 +1808,14 @@
         <v>120</v>
       </c>
     </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>121</v>
+      </c>
+      <c r="C94" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49805F4B-7F19-498A-AC71-2CD4C1185F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5BE5AB-410B-475A-B8BE-6D0A9B252B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="124">
   <si>
     <t>对象</t>
   </si>
@@ -483,6 +483,14 @@
   </si>
   <si>
     <t>功能优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现mod物品堆叠、快捷操作p1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -833,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1093,6 +1101,9 @@
       <c r="B24" t="s">
         <v>28</v>
       </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -1343,6 +1354,9 @@
       <c r="B47" t="s">
         <v>54</v>
       </c>
+      <c r="C47" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1395,6 +1409,9 @@
       <c r="B52" t="s">
         <v>61</v>
       </c>
+      <c r="C52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1641,6 +1658,9 @@
       <c r="B76" t="s">
         <v>96</v>
       </c>
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1812,8 +1832,19 @@
       <c r="A94" t="s">
         <v>121</v>
       </c>
+      <c r="B94" t="s">
+        <v>122</v>
+      </c>
       <c r="C94" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>123</v>
+      </c>
+      <c r="C95" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5BE5AB-410B-475A-B8BE-6D0A9B252B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484301D1-D2C1-4D7C-96F7-75D60F5B5E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="126">
   <si>
     <t>对象</t>
   </si>
@@ -491,6 +491,14 @@
   </si>
   <si>
     <t>实现mod物品堆叠、快捷操作p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现mod物品堆叠、快捷操作p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -841,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1843,8 +1851,19 @@
       <c r="A95" t="s">
         <v>123</v>
       </c>
+      <c r="B95" t="s">
+        <v>122</v>
+      </c>
       <c r="C95" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484301D1-D2C1-4D7C-96F7-75D60F5B5E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D53180D-7259-4A32-8559-9616F0347A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="127">
   <si>
     <t>对象</t>
   </si>
@@ -499,6 +499,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐私读控nbt写入不过滤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -849,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1866,6 +1870,11 @@
         <v>125</v>
       </c>
     </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D53180D-7259-4A32-8559-9616F0347A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F31F42-8980-429F-B1BD-6DE4AE50C9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="129">
   <si>
     <t>对象</t>
   </si>
@@ -503,6 +503,14 @@
   </si>
   <si>
     <t>隐私读控nbt写入不过滤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速连接工具第一版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -853,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
@@ -1870,9 +1878,17 @@
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>127</v>
+      </c>
+      <c r="C98" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F31F42-8980-429F-B1BD-6DE4AE50C9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FD91B5-389A-43B5-82B6-5CCA99D337A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="130">
   <si>
     <t>对象</t>
   </si>
@@ -294,10 +294,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>信号链路一致性增强*p8-p9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>核心粉去原版依赖补做</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -507,6 +503,14 @@
   </si>
   <si>
     <t>快速连接工具第一版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速连接工具第二版</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -864,7 +868,7 @@
   <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="1" max="1" width="53.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1122,7 +1126,7 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,7 +1379,7 @@
         <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1430,7 +1434,7 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1504,7 +1508,7 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
         <v>69</v>
@@ -1512,29 +1516,35 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="B60" t="s">
-        <v>79</v>
-      </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>74</v>
       </c>
+      <c r="B61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1542,10 +1552,10 @@
         <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,10 +1563,10 @@
         <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1564,21 +1574,18 @@
         <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>83</v>
       </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1586,45 +1593,48 @@
         <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>85</v>
       </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>86</v>
       </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>96</v>
+      </c>
+      <c r="B70" t="s">
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1632,43 +1642,43 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>91</v>
+      <c r="A74" t="s">
+        <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1676,10 +1686,10 @@
         <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1687,32 +1697,32 @@
         <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" t="s">
         <v>95</v>
       </c>
-      <c r="B78" t="s">
-        <v>92</v>
-      </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1720,10 +1730,10 @@
         <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1731,150 +1741,144 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83" t="s">
         <v>104</v>
       </c>
-      <c r="B83" t="s">
-        <v>105</v>
-      </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>106</v>
       </c>
-      <c r="B84" t="s">
-        <v>105</v>
-      </c>
       <c r="C84" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="B87" t="s">
+        <v>113</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>113</v>
-      </c>
-      <c r="B88" t="s">
         <v>114</v>
       </c>
       <c r="C88" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>115</v>
       </c>
+      <c r="B89" t="s">
+        <v>116</v>
+      </c>
       <c r="C89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>117</v>
+      </c>
+      <c r="B90" t="s">
         <v>116</v>
       </c>
-      <c r="B90" t="s">
-        <v>117</v>
-      </c>
       <c r="C90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>118</v>
       </c>
-      <c r="B91" t="s">
-        <v>117</v>
-      </c>
       <c r="C91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>119</v>
       </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>120</v>
       </c>
+      <c r="B93" t="s">
+        <v>121</v>
+      </c>
+      <c r="C93" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" t="s">
         <v>121</v>
       </c>
-      <c r="B94" t="s">
-        <v>122</v>
-      </c>
       <c r="C94" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>123</v>
       </c>
-      <c r="B95" t="s">
-        <v>122</v>
-      </c>
       <c r="C95" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>124</v>
-      </c>
-      <c r="C96" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1882,13 +1886,16 @@
       <c r="A97" t="s">
         <v>126</v>
       </c>
+      <c r="C97" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FD91B5-389A-43B5-82B6-5CCA99D337A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37B3CE3-889F-498B-8A36-C8B99CE9FB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="131">
   <si>
     <t>对象</t>
   </si>
@@ -515,6 +515,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增同步遥控器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -865,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1898,6 +1902,14 @@
         <v>129</v>
       </c>
     </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37B3CE3-889F-498B-8A36-C8B99CE9FB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D35DB6-1FAF-401A-AE8F-2C7C2BACDF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5136" yWindow="3816" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="4008" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="133">
   <si>
     <t>对象</t>
   </si>
@@ -519,6 +519,14 @@
   </si>
   <si>
     <t>新增同步遥控器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linker退役缺口补齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区块加卸载感知重构</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -869,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1910,6 +1918,19 @@
         <v>129</v>
       </c>
     </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C100" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D35DB6-1FAF-401A-AE8F-2C7C2BACDF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A542AA-B0C4-4C01-92C7-46EE0BE7E7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="4008" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5208" yWindow="2328" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="134">
   <si>
     <t>对象</t>
   </si>
@@ -70,9 +70,6 @@
     <t>分层自动化测试与回归基线迁移</t>
   </si>
   <si>
-    <t>f</t>
-  </si>
-  <si>
     <t>GUI 当前匹配显示截断与 tooltip 提示</t>
   </si>
   <si>
@@ -527,6 +524,14 @@
   </si>
   <si>
     <t>区块加卸载感知重构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补齐快速连接工具的缓存上传长度保护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态面板第一版</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -877,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1014,40 +1019,40 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -1055,10 +1060,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -1066,10 +1071,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -1077,10 +1082,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
         <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -1099,836 +1104,864 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
         <v>31</v>
-      </c>
-      <c r="B25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
         <v>38</v>
       </c>
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s">
         <v>48</v>
       </c>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
         <v>50</v>
       </c>
-      <c r="B40" t="s">
-        <v>51</v>
-      </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
         <v>60</v>
       </c>
-      <c r="B48" t="s">
-        <v>61</v>
-      </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" t="s">
         <v>68</v>
-      </c>
-      <c r="B55" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" t="s">
         <v>77</v>
       </c>
-      <c r="B60" t="s">
-        <v>78</v>
-      </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" t="s">
         <v>90</v>
       </c>
-      <c r="B73" t="s">
-        <v>91</v>
-      </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" t="s">
         <v>94</v>
-      </c>
-      <c r="B77" t="s">
-        <v>91</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" t="s">
         <v>101</v>
       </c>
-      <c r="B81" t="s">
-        <v>102</v>
-      </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" t="s">
         <v>103</v>
       </c>
-      <c r="B82" t="s">
-        <v>104</v>
-      </c>
       <c r="C82" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84" t="s">
         <v>106</v>
-      </c>
-      <c r="C84" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" t="s">
         <v>108</v>
-      </c>
-      <c r="C85" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" t="s">
         <v>110</v>
-      </c>
-      <c r="C86" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87" t="s">
         <v>112</v>
       </c>
-      <c r="B87" t="s">
-        <v>113</v>
-      </c>
       <c r="C87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" t="s">
         <v>115</v>
       </c>
-      <c r="B89" t="s">
-        <v>116</v>
-      </c>
       <c r="C89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="C92" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" t="s">
         <v>120</v>
       </c>
-      <c r="B93" t="s">
-        <v>121</v>
-      </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C94" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>122</v>
+      </c>
+      <c r="C95" t="s">
         <v>123</v>
-      </c>
-      <c r="C95" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="B96" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>125</v>
+      </c>
+      <c r="B97" t="s">
+        <v>128</v>
+      </c>
+      <c r="C97" t="s">
         <v>126</v>
-      </c>
-      <c r="C97" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>127</v>
+      </c>
+      <c r="B98" t="s">
         <v>128</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>132</v>
+      </c>
+      <c r="B102" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C103" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A542AA-B0C4-4C01-92C7-46EE0BE7E7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ED06B0-BC0B-4A99-AB82-BF1A1EEC66DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5208" yWindow="2328" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
   <si>
     <t>对象</t>
   </si>
@@ -532,6 +532,14 @@
   </si>
   <si>
     <t>状态面板第一版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态面板第二版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -882,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1964,6 +1972,14 @@
         <v>128</v>
       </c>
     </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>134</v>
+      </c>
+      <c r="C104" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ED06B0-BC0B-4A99-AB82-BF1A1EEC66DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED23141-4815-4CBF-A658-949646E504C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5208" yWindow="2328" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="137">
   <si>
     <t>对象</t>
   </si>
@@ -540,6 +540,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui层结构优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -890,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1980,6 +1984,14 @@
         <v>135</v>
       </c>
     </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>136</v>
+      </c>
+      <c r="C105" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED23141-4815-4CBF-A658-949646E504C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84254B44-D250-4F42-938C-2630B0CF7CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5208" yWindow="2328" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="139">
   <si>
     <t>对象</t>
   </si>
@@ -544,6 +544,14 @@
   </si>
   <si>
     <t>gui层结构优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复创造模式tooltip归属字段缺失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -894,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -1992,6 +2000,14 @@
         <v>135</v>
       </c>
     </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84254B44-D250-4F42-938C-2630B0CF7CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286E9A1-BBA6-46A8-A604-6EC1702790B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="140">
   <si>
     <t>对象</t>
   </si>
@@ -552,6 +552,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态面板补全隐私读控</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -902,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2008,6 +2012,11 @@
         <v>138</v>
       </c>
     </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286E9A1-BBA6-46A8-A604-6EC1702790B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C07DDF-8973-4A28-AD08-28694E18B843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="141">
   <si>
     <t>对象</t>
   </si>
@@ -556,6 +556,10 @@
   </si>
   <si>
     <t>状态面板补全隐私读控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期调度管线重构p1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2017,6 +2021,14 @@
         <v>139</v>
       </c>
     </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C07DDF-8973-4A28-AD08-28694E18B843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D73320-59A8-4A5A-AD66-2DB7F9BBECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="142">
   <si>
     <t>对象</t>
   </si>
@@ -560,6 +560,10 @@
   </si>
   <si>
     <t>生命周期调度管线重构p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期调度管线重构p2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -910,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2029,6 +2033,11 @@
         <v>138</v>
       </c>
     </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D73320-59A8-4A5A-AD66-2DB7F9BBECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76881FCF-ED22-470C-85DF-3F35C75178E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="143">
   <si>
     <t>对象</t>
   </si>
@@ -564,6 +564,10 @@
   </si>
   <si>
     <t>生命周期调度管线重构p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1979,6 +1983,9 @@
       <c r="A101" t="s">
         <v>131</v>
       </c>
+      <c r="C101" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
@@ -2036,6 +2043,9 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>141</v>
+      </c>
+      <c r="C109" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76881FCF-ED22-470C-85DF-3F35C75178E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA57669-02D2-4214-8427-D628AAFB8B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="146">
   <si>
     <t>对象</t>
   </si>
@@ -568,6 +568,18 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期调度管线重构补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包优化接入调度层p1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包优化接入调度层p3/4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2048,6 +2060,27 @@
         <v>142</v>
       </c>
     </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA57669-02D2-4214-8427-D628AAFB8B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4BD2F-5178-4F36-95D0-C47F5F38FCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="147">
   <si>
     <t>对象</t>
   </si>
@@ -580,6 +580,10 @@
   </si>
   <si>
     <t>批打包优化接入调度层p3/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包优化接入调度层p5/6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -930,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2080,6 +2084,14 @@
       <c r="A112" t="s">
         <v>145</v>
       </c>
+      <c r="C112" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4BD2F-5178-4F36-95D0-C47F5F38FCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1B2A38-D84F-4356-9BBA-863F29B67232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="148">
   <si>
     <t>对象</t>
   </si>
@@ -584,6 +584,10 @@
   </si>
   <si>
     <t>批打包优化接入调度层p5/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2088,9 +2092,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>146</v>
+      </c>
+      <c r="C113" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1B2A38-D84F-4356-9BBA-863F29B67232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEC1905-DC62-47E3-9A67-20E0045AF48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
   <si>
     <t>对象</t>
   </si>
@@ -588,6 +588,18 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包内存优化p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包游戏内测试用例补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 批打包优化接入调度层p7/8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -938,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2100,6 +2112,30 @@
         <v>147</v>
       </c>
     </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>148</v>
+      </c>
+      <c r="C114" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>149</v>
+      </c>
+      <c r="C115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>150</v>
+      </c>
+      <c r="C116" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEC1905-DC62-47E3-9A67-20E0045AF48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF020CD4-931B-49D1-955D-F1436C2EF1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="151">
   <si>
     <t>对象</t>
   </si>
@@ -1961,6 +1961,9 @@
       <c r="A95" t="s">
         <v>122</v>
       </c>
+      <c r="B95" t="s">
+        <v>147</v>
+      </c>
       <c r="C95" t="s">
         <v>123</v>
       </c>
@@ -1999,6 +2002,9 @@
       <c r="A99" t="s">
         <v>129</v>
       </c>
+      <c r="B99" t="s">
+        <v>147</v>
+      </c>
       <c r="C99" t="s">
         <v>128</v>
       </c>
@@ -2031,6 +2037,9 @@
       <c r="A103" t="s">
         <v>133</v>
       </c>
+      <c r="B103" t="s">
+        <v>147</v>
+      </c>
       <c r="C103" t="s">
         <v>128</v>
       </c>
@@ -2038,6 +2047,9 @@
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>134</v>
+      </c>
+      <c r="B104" t="s">
+        <v>147</v>
       </c>
       <c r="C104" t="s">
         <v>135</v>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF020CD4-931B-49D1-955D-F1436C2EF1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C179A-D388-46DE-8E5A-A76FA629F9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="2772" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="153">
   <si>
     <t>对象</t>
   </si>
@@ -600,6 +600,14 @@
   </si>
   <si>
     <t>## 批打包优化接入调度层p7/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 高并发延迟采集与所需处理窗口推算p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 高并发延迟采集与所需处理窗口推算p2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -950,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2148,6 +2156,22 @@
         <v>147</v>
       </c>
     </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>151</v>
+      </c>
+      <c r="C117" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>152</v>
+      </c>
+      <c r="C118" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C179A-D388-46DE-8E5A-A76FA629F9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B0397C-B315-41CB-AFC5-8296E50C8E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="156">
   <si>
     <t>对象</t>
   </si>
@@ -608,6 +608,18 @@
   </si>
   <si>
     <t>## 高并发延迟采集与所需处理窗口推算p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>## toggle/pulse非生命周期链路接入批打包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 批打包补测mixed,windows=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -958,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2172,6 +2184,22 @@
         <v>147</v>
       </c>
     </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="C119" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>154</v>
+      </c>
+      <c r="C120" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B0397C-B315-41CB-AFC5-8296E50C8E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AF3B44-DBCA-495A-9264-E643C9AA3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="158">
   <si>
     <t>对象</t>
   </si>
@@ -620,6 +620,14 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">## </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2033,6 +2041,9 @@
       <c r="A100" t="s">
         <v>130</v>
       </c>
+      <c r="B100" t="s">
+        <v>156</v>
+      </c>
       <c r="C100" t="s">
         <v>128</v>
       </c>
@@ -2041,6 +2052,9 @@
       <c r="A101" t="s">
         <v>131</v>
       </c>
+      <c r="B101" t="s">
+        <v>156</v>
+      </c>
       <c r="C101" t="s">
         <v>142</v>
       </c>
@@ -2079,6 +2093,9 @@
       <c r="A105" t="s">
         <v>136</v>
       </c>
+      <c r="B105" t="s">
+        <v>156</v>
+      </c>
       <c r="C105" t="s">
         <v>135</v>
       </c>
@@ -2087,6 +2104,9 @@
       <c r="A106" t="s">
         <v>137</v>
       </c>
+      <c r="B106" t="s">
+        <v>156</v>
+      </c>
       <c r="C106" t="s">
         <v>138</v>
       </c>
@@ -2095,11 +2115,17 @@
       <c r="A107" t="s">
         <v>139</v>
       </c>
+      <c r="B107" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>140</v>
       </c>
+      <c r="B108" t="s">
+        <v>156</v>
+      </c>
       <c r="C108" t="s">
         <v>138</v>
       </c>
@@ -2108,6 +2134,9 @@
       <c r="A109" t="s">
         <v>141</v>
       </c>
+      <c r="B109" t="s">
+        <v>156</v>
+      </c>
       <c r="C109" t="s">
         <v>142</v>
       </c>
@@ -2116,6 +2145,9 @@
       <c r="A110" t="s">
         <v>143</v>
       </c>
+      <c r="B110" t="s">
+        <v>156</v>
+      </c>
       <c r="C110" t="s">
         <v>142</v>
       </c>
@@ -2124,6 +2156,9 @@
       <c r="A111" t="s">
         <v>144</v>
       </c>
+      <c r="B111" t="s">
+        <v>156</v>
+      </c>
       <c r="C111" t="s">
         <v>142</v>
       </c>
@@ -2132,6 +2167,9 @@
       <c r="A112" t="s">
         <v>145</v>
       </c>
+      <c r="B112" t="s">
+        <v>156</v>
+      </c>
       <c r="C112" t="s">
         <v>142</v>
       </c>
@@ -2140,6 +2178,9 @@
       <c r="A113" t="s">
         <v>146</v>
       </c>
+      <c r="B113" t="s">
+        <v>156</v>
+      </c>
       <c r="C113" t="s">
         <v>147</v>
       </c>
@@ -2148,6 +2189,9 @@
       <c r="A114" t="s">
         <v>148</v>
       </c>
+      <c r="B114" t="s">
+        <v>156</v>
+      </c>
       <c r="C114" t="s">
         <v>147</v>
       </c>
@@ -2156,6 +2200,9 @@
       <c r="A115" t="s">
         <v>149</v>
       </c>
+      <c r="B115" t="s">
+        <v>156</v>
+      </c>
       <c r="C115" t="s">
         <v>147</v>
       </c>
@@ -2164,6 +2211,9 @@
       <c r="A116" t="s">
         <v>150</v>
       </c>
+      <c r="B116" t="s">
+        <v>156</v>
+      </c>
       <c r="C116" t="s">
         <v>147</v>
       </c>
@@ -2172,6 +2222,9 @@
       <c r="A117" t="s">
         <v>151</v>
       </c>
+      <c r="B117" t="s">
+        <v>156</v>
+      </c>
       <c r="C117" t="s">
         <v>147</v>
       </c>
@@ -2180,6 +2233,9 @@
       <c r="A118" t="s">
         <v>152</v>
       </c>
+      <c r="B118" t="s">
+        <v>156</v>
+      </c>
       <c r="C118" t="s">
         <v>147</v>
       </c>
@@ -2188,6 +2244,9 @@
       <c r="A119" t="s">
         <v>153</v>
       </c>
+      <c r="B119" t="s">
+        <v>156</v>
+      </c>
       <c r="C119" t="s">
         <v>155</v>
       </c>
@@ -2196,8 +2255,16 @@
       <c r="A120" t="s">
         <v>154</v>
       </c>
+      <c r="B120" t="s">
+        <v>156</v>
+      </c>
       <c r="C120" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AF3B44-DBCA-495A-9264-E643C9AA3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF84F78-242F-4CC4-8339-4FFCE5448B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1716" yWindow="3636" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="161">
   <si>
     <t>对象</t>
   </si>
@@ -599,35 +599,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>## 批打包优化接入调度层p7/8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## 高并发延迟采集与所需处理窗口推算p1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## 高并发延迟采集与所需处理窗口推算p2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## toggle/pulse非生命周期链路接入批打包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## 批打包补测mixed,windows=0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">## </t>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络端重构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>core配对payload统一到结构化包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨区块总量上限与背压拒绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复r05测试偏差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包补测mixed,windows=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toggle/pulse非生命周期链路接入批打包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高并发延迟采集与所需处理窗口推算p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高并发延迟采集与所需处理窗口推算p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批打包优化接入调度层p7/8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -978,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2042,7 +2054,7 @@
         <v>130</v>
       </c>
       <c r="B100" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C100" t="s">
         <v>128</v>
@@ -2053,7 +2065,7 @@
         <v>131</v>
       </c>
       <c r="B101" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C101" t="s">
         <v>142</v>
@@ -2094,7 +2106,7 @@
         <v>136</v>
       </c>
       <c r="B105" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C105" t="s">
         <v>135</v>
@@ -2105,7 +2117,7 @@
         <v>137</v>
       </c>
       <c r="B106" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C106" t="s">
         <v>138</v>
@@ -2116,7 +2128,7 @@
         <v>139</v>
       </c>
       <c r="B107" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2124,7 +2136,7 @@
         <v>140</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C108" t="s">
         <v>138</v>
@@ -2135,7 +2147,7 @@
         <v>141</v>
       </c>
       <c r="B109" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C109" t="s">
         <v>142</v>
@@ -2146,7 +2158,7 @@
         <v>143</v>
       </c>
       <c r="B110" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C110" t="s">
         <v>142</v>
@@ -2157,7 +2169,7 @@
         <v>144</v>
       </c>
       <c r="B111" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C111" t="s">
         <v>142</v>
@@ -2168,7 +2180,7 @@
         <v>145</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C112" t="s">
         <v>142</v>
@@ -2179,7 +2191,7 @@
         <v>146</v>
       </c>
       <c r="B113" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C113" t="s">
         <v>147</v>
@@ -2190,7 +2202,7 @@
         <v>148</v>
       </c>
       <c r="B114" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C114" t="s">
         <v>147</v>
@@ -2201,7 +2213,7 @@
         <v>149</v>
       </c>
       <c r="B115" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C115" t="s">
         <v>147</v>
@@ -2209,10 +2221,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B116" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
         <v>147</v>
@@ -2220,10 +2232,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B117" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C117" t="s">
         <v>147</v>
@@ -2231,10 +2243,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C118" t="s">
         <v>147</v>
@@ -2242,29 +2254,68 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B119" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B120" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C120" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>155</v>
+      </c>
+      <c r="B121" t="s">
+        <v>151</v>
+      </c>
+      <c r="C121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>152</v>
+      </c>
+      <c r="B122" t="s">
+        <v>151</v>
+      </c>
+      <c r="C122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>153</v>
+      </c>
+      <c r="B123" t="s">
+        <v>151</v>
+      </c>
+      <c r="C123" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>154</v>
+      </c>
+      <c r="B124" t="s">
+        <v>151</v>
+      </c>
+      <c r="C124" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF84F78-242F-4CC4-8339-4FFCE5448B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF3D4C3-5D8C-4E5E-804A-B4627301512F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1716" yWindow="3636" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6420" yWindow="2172" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="164">
   <si>
     <t>对象</t>
   </si>
@@ -640,6 +640,18 @@
   </si>
   <si>
     <t>批打包优化接入调度层p7/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补发flush重入修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图写并发控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -990,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2318,6 +2330,39 @@
         <v>151</v>
       </c>
     </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>161</v>
+      </c>
+      <c r="B125" t="s">
+        <v>151</v>
+      </c>
+      <c r="C125" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" t="s">
+        <v>151</v>
+      </c>
+      <c r="C126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>163</v>
+      </c>
+      <c r="B127" t="s">
+        <v>151</v>
+      </c>
+      <c r="C127" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF3D4C3-5D8C-4E5E-804A-B4627301512F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98135899-4D28-46F0-B209-D368EA22E4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="2172" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="165">
   <si>
     <t>对象</t>
   </si>
@@ -652,6 +652,10 @@
   </si>
   <si>
     <t>中文名优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近外显补充跨区块身份</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1002,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2363,6 +2367,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>164</v>
+      </c>
+      <c r="C128" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98135899-4D28-46F0-B209-D368EA22E4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE3EA14-7EF5-4115-A4A5-0CCCC8B91459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="2172" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="166">
   <si>
     <t>对象</t>
   </si>
@@ -656,6 +656,10 @@
   </si>
   <si>
     <t>近外显补充跨区块身份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成就系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1006,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2375,6 +2379,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>165</v>
+      </c>
+      <c r="C129" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE3EA14-7EF5-4115-A4A5-0CCCC8B91459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AECF867-109F-4A16-BB87-611E3BA01584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="2172" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="167">
   <si>
     <t>对象</t>
   </si>
@@ -660,6 +660,10 @@
   </si>
   <si>
     <t>成就系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复配方和dataGen缺陷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1010,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2387,6 +2391,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>166</v>
+      </c>
+      <c r="C130" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AECF867-109F-4A16-BB87-611E3BA01584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5353BD63-9C47-4649-A852-1C8A8CF089F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="2172" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="169">
   <si>
     <t>对象</t>
   </si>
@@ -664,6 +664,14 @@
   </si>
   <si>
     <t>修复配方和dataGen缺陷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速连接工具接入OCC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1014,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2399,6 +2407,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5353BD63-9C47-4649-A852-1C8A8CF089F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC72D3-B9F8-4957-B54C-E1D10E6BD791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="170">
   <si>
     <t>对象</t>
   </si>
@@ -672,6 +672,10 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCC补测</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1022,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2414,6 +2418,17 @@
       <c r="B131" t="s">
         <v>168</v>
       </c>
+      <c r="C131" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>169</v>
+      </c>
+      <c r="C132" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC72D3-B9F8-4957-B54C-E1D10E6BD791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB44922-4900-403F-B83B-5623BB3C1D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5256" yWindow="2928" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="171">
   <si>
     <t>对象</t>
   </si>
@@ -676,6 +676,10 @@
   </si>
   <si>
     <t>OCC补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史语义清理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1026,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2391,6 +2395,9 @@
       <c r="A128" t="s">
         <v>164</v>
       </c>
+      <c r="B128" t="s">
+        <v>168</v>
+      </c>
       <c r="C128" t="s">
         <v>151</v>
       </c>
@@ -2399,6 +2406,9 @@
       <c r="A129" t="s">
         <v>165</v>
       </c>
+      <c r="B129" t="s">
+        <v>168</v>
+      </c>
       <c r="C129" t="s">
         <v>151</v>
       </c>
@@ -2407,6 +2417,9 @@
       <c r="A130" t="s">
         <v>166</v>
       </c>
+      <c r="B130" t="s">
+        <v>168</v>
+      </c>
       <c r="C130" t="s">
         <v>151</v>
       </c>
@@ -2426,7 +2439,21 @@
       <c r="A132" t="s">
         <v>169</v>
       </c>
+      <c r="B132" t="s">
+        <v>168</v>
+      </c>
       <c r="C132" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>170</v>
+      </c>
+      <c r="B133" t="s">
+        <v>168</v>
+      </c>
+      <c r="C133" t="s">
         <v>168</v>
       </c>
     </row>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB44922-4900-403F-B83B-5623BB3C1D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A95E2-66E5-4A18-82DB-F29D1FCEA4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
   <si>
     <t>对象</t>
   </si>
@@ -680,6 +680,10 @@
   </si>
   <si>
     <t>历史语义清理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务端单端基本兼容性测试/针对性压测</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1030,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2457,6 +2461,17 @@
         <v>168</v>
       </c>
     </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>171</v>
+      </c>
+      <c r="B134" t="s">
+        <v>168</v>
+      </c>
+      <c r="C134" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A95E2-66E5-4A18-82DB-F29D1FCEA4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F781FE3-1D39-4EC7-AF34-511E5794F0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F781FE3-1D39-4EC7-AF34-511E5794F0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829A2A85-E2A2-4288-B143-0D26603F48BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="177">
   <si>
     <t>对象</t>
   </si>
@@ -684,6 +684,26 @@
   </si>
   <si>
     <t>服务端单端基本兼容性测试/针对性压测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>core occ粒度优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occ 多端测试以及游戏内补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成就性能优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贴图命名规范化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1034,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2472,6 +2492,44 @@
         <v>168</v>
       </c>
     </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>172</v>
+      </c>
+      <c r="C135" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>173</v>
+      </c>
+      <c r="B136" t="s">
+        <v>175</v>
+      </c>
+      <c r="C136" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>174</v>
+      </c>
+      <c r="C137" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>176</v>
+      </c>
+      <c r="B138" t="s">
+        <v>175</v>
+      </c>
+      <c r="C138" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829A2A85-E2A2-4288-B143-0D26603F48BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BD0C73-FEC7-470E-91E4-F45655939A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="178">
   <si>
     <t>对象</t>
   </si>
@@ -704,6 +704,10 @@
   </si>
   <si>
     <t>贴图命名规范化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复core occ传参错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1054,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2530,6 +2534,17 @@
         <v>175</v>
       </c>
     </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>177</v>
+      </c>
+      <c r="B139" t="s">
+        <v>175</v>
+      </c>
+      <c r="C139" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BD0C73-FEC7-470E-91E4-F45655939A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9882E9-341E-4602-B485-2B8508F12D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="179">
   <si>
     <t>对象</t>
   </si>
@@ -708,6 +708,10 @@
   </si>
   <si>
     <t>修复core occ传参错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复近外显节流跨存档冷却时间点残留</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1058,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2545,6 +2549,14 @@
         <v>175</v>
       </c>
     </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>178</v>
+      </c>
+      <c r="C140" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9882E9-341E-4602-B485-2B8508F12D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C00333E-26C3-4537-999A-AB3AD19FE4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C00333E-26C3-4537-999A-AB3AD19FE4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A57BBF7-26DE-4508-86D2-E361AEFC356B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="179">
   <si>
     <t>对象</t>
   </si>
@@ -2504,6 +2504,9 @@
       <c r="A135" t="s">
         <v>172</v>
       </c>
+      <c r="B135" t="s">
+        <v>175</v>
+      </c>
       <c r="C135" t="s">
         <v>175</v>
       </c>
@@ -2523,6 +2526,9 @@
       <c r="A137" t="s">
         <v>174</v>
       </c>
+      <c r="B137" t="s">
+        <v>175</v>
+      </c>
       <c r="C137" t="s">
         <v>175</v>
       </c>
@@ -2552,6 +2558,9 @@
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>178</v>
+      </c>
+      <c r="B140" t="s">
+        <v>175</v>
       </c>
       <c r="C140" t="s">
         <v>175</v>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A57BBF7-26DE-4508-86D2-E361AEFC356B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C578190D-22E5-4F2D-BF33-FE7BA62DBA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5424" yWindow="2988" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9696" yWindow="2184" windowWidth="12696" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="193">
   <si>
     <t>对象</t>
   </si>
@@ -712,6 +712,62 @@
   </si>
   <si>
     <t>修复近外显节流跨存档冷却时间点残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重构core抽象基类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快照性能优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器第一版p6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器游戏内补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速连接工具对接过滤器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器文档同步修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui美化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>压力场景下过滤器性能与功能补测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1062,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.21875" customWidth="1"/>
@@ -2566,6 +2622,116 @@
         <v>175</v>
       </c>
     </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>179</v>
+      </c>
+      <c r="B141" t="s">
+        <v>192</v>
+      </c>
+      <c r="C141" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>180</v>
+      </c>
+      <c r="B142" t="s">
+        <v>192</v>
+      </c>
+      <c r="C142" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>181</v>
+      </c>
+      <c r="C143" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>182</v>
+      </c>
+      <c r="C144" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>183</v>
+      </c>
+      <c r="C145" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>184</v>
+      </c>
+      <c r="C146" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>185</v>
+      </c>
+      <c r="C147" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>186</v>
+      </c>
+      <c r="C148" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>187</v>
+      </c>
+      <c r="C149" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>188</v>
+      </c>
+      <c r="C150" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>189</v>
+      </c>
+      <c r="C151" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>190</v>
+      </c>
+      <c r="C152" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>191</v>
+      </c>
+      <c r="C153" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs_dev/审查日志与测试记录.xlsx
+++ b/docs_dev/审查日志与测试记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-no-mixin\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C578190D-22E5-4F2D-BF33-FE7BA62DBA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEAD245-8CD8-49FD-BA46-330E5B79F058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9696" yWindow="2184" windowWidth="12696" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="193">
   <si>
     <t>对象</t>
   </si>
@@ -2648,6 +2648,9 @@
       <c r="A143" t="s">
         <v>181</v>
       </c>
+      <c r="B143" t="s">
+        <v>192</v>
+      </c>
       <c r="C143" t="s">
         <v>192</v>
       </c>
@@ -2656,6 +2659,9 @@
       <c r="A144" t="s">
         <v>182</v>
       </c>
+      <c r="B144" t="s">
+        <v>192</v>
+      </c>
       <c r="C144" t="s">
         <v>192</v>
       </c>
@@ -2664,6 +2670,9 @@
       <c r="A145" t="s">
         <v>183</v>
       </c>
+      <c r="B145" t="s">
+        <v>192</v>
+      </c>
       <c r="C145" t="s">
         <v>192</v>
       </c>
@@ -2672,6 +2681,9 @@
       <c r="A146" t="s">
         <v>184</v>
       </c>
+      <c r="B146" t="s">
+        <v>192</v>
+      </c>
       <c r="C146" t="s">
         <v>192</v>
       </c>
@@ -2680,6 +2692,9 @@
       <c r="A147" t="s">
         <v>185</v>
       </c>
+      <c r="B147" t="s">
+        <v>192</v>
+      </c>
       <c r="C147" t="s">
         <v>192</v>
       </c>
@@ -2688,6 +2703,9 @@
       <c r="A148" t="s">
         <v>186</v>
       </c>
+      <c r="B148" t="s">
+        <v>192</v>
+      </c>
       <c r="C148" t="s">
         <v>192</v>
       </c>
@@ -2696,6 +2714,9 @@
       <c r="A149" t="s">
         <v>187</v>
       </c>
+      <c r="B149" t="s">
+        <v>192</v>
+      </c>
       <c r="C149" t="s">
         <v>192</v>
       </c>
@@ -2704,6 +2725,9 @@
       <c r="A150" t="s">
         <v>188</v>
       </c>
+      <c r="B150" t="s">
+        <v>192</v>
+      </c>
       <c r="C150" t="s">
         <v>192</v>
       </c>
@@ -2712,6 +2736,9 @@
       <c r="A151" t="s">
         <v>189</v>
       </c>
+      <c r="B151" t="s">
+        <v>192</v>
+      </c>
       <c r="C151" t="s">
         <v>192</v>
       </c>
@@ -2720,6 +2747,9 @@
       <c r="A152" t="s">
         <v>190</v>
       </c>
+      <c r="B152" t="s">
+        <v>192</v>
+      </c>
       <c r="C152" t="s">
         <v>192</v>
       </c>
@@ -2727,6 +2757,9 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>191</v>
+      </c>
+      <c r="B153" t="s">
+        <v>192</v>
       </c>
       <c r="C153" t="s">
         <v>192</v>
